--- a/Automation/Cypress_Automation/Cypress/results/Create-note-data-TC-2.xlsx
+++ b/Automation/Cypress_Automation/Cypress/results/Create-note-data-TC-2.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,26 @@
         <v>Completed</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Supereme Karki</v>
+      </c>
+      <c r="B3" t="str">
+        <v>supreme@yopmail.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Admin@123</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-20T03:28:32.254Z</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>